--- a/MAPAS/mapas.xlsx
+++ b/MAPAS/mapas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tomy\Documents\GitHub\GAME\MAPAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8077EBB-5049-405F-BE39-F396E650E338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD497BB0-A017-4C8C-BC4D-A7A162221802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{BD767282-5304-4F62-A220-83AC4A12E812}"/>
   </bookViews>
@@ -739,7 +739,51 @@
     <cellStyle name="Título 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="18">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1665,7 +1709,7 @@
     </row>
     <row r="7" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
@@ -5822,28 +5866,1470 @@
       <c r="X60" s="1"/>
       <c r="Y60" s="1"/>
     </row>
-    <row r="61" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>0</v>
+      </c>
+      <c r="B61" s="1">
+        <v>0</v>
+      </c>
+      <c r="C61" s="1">
+        <v>0</v>
+      </c>
+      <c r="D61" s="1">
+        <v>0</v>
+      </c>
+      <c r="E61" s="1">
+        <v>0</v>
+      </c>
+      <c r="F61" s="1">
+        <v>0</v>
+      </c>
+      <c r="G61" s="1">
+        <v>0</v>
+      </c>
+      <c r="H61" s="1">
+        <v>0</v>
+      </c>
+      <c r="I61" s="1">
+        <v>0</v>
+      </c>
+      <c r="J61" s="1">
+        <v>0</v>
+      </c>
+      <c r="K61" s="1">
+        <v>0</v>
+      </c>
+      <c r="L61" s="1">
+        <v>0</v>
+      </c>
+      <c r="M61" s="1">
+        <v>0</v>
+      </c>
+      <c r="N61" s="1">
+        <v>0</v>
+      </c>
+      <c r="O61" s="1">
+        <v>0</v>
+      </c>
+      <c r="P61" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="1">
+        <v>0</v>
+      </c>
+      <c r="R61" s="1">
+        <v>0</v>
+      </c>
+      <c r="S61" s="1">
+        <v>0</v>
+      </c>
+      <c r="T61" s="1">
+        <v>0</v>
+      </c>
+      <c r="U61" s="1">
+        <v>0</v>
+      </c>
+      <c r="V61" s="1">
+        <v>0</v>
+      </c>
+      <c r="W61" s="1">
+        <v>0</v>
+      </c>
+      <c r="X61" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>0</v>
+      </c>
+      <c r="B62" s="1">
+        <v>0</v>
+      </c>
+      <c r="C62" s="1">
+        <v>0</v>
+      </c>
+      <c r="D62" s="1">
+        <v>0</v>
+      </c>
+      <c r="E62" s="1">
+        <v>0</v>
+      </c>
+      <c r="F62" s="1">
+        <v>0</v>
+      </c>
+      <c r="G62" s="1">
+        <v>0</v>
+      </c>
+      <c r="H62" s="1">
+        <v>0</v>
+      </c>
+      <c r="I62" s="1">
+        <v>0</v>
+      </c>
+      <c r="J62" s="1">
+        <v>0</v>
+      </c>
+      <c r="K62" s="1">
+        <v>0</v>
+      </c>
+      <c r="L62" s="1">
+        <v>0</v>
+      </c>
+      <c r="M62" s="1">
+        <v>0</v>
+      </c>
+      <c r="N62" s="1">
+        <v>0</v>
+      </c>
+      <c r="O62" s="1">
+        <v>0</v>
+      </c>
+      <c r="P62" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="1">
+        <v>0</v>
+      </c>
+      <c r="R62" s="1">
+        <v>0</v>
+      </c>
+      <c r="S62" s="1">
+        <v>0</v>
+      </c>
+      <c r="T62" s="1">
+        <v>0</v>
+      </c>
+      <c r="U62" s="1">
+        <v>0</v>
+      </c>
+      <c r="V62" s="1">
+        <v>0</v>
+      </c>
+      <c r="W62" s="1">
+        <v>0</v>
+      </c>
+      <c r="X62" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="1">
+        <v>0</v>
+      </c>
+    </row>
     <row r="63" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M63" s="14"/>
-    </row>
-    <row r="64" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="A63" s="1">
+        <v>0</v>
+      </c>
+      <c r="B63" s="1">
+        <v>0</v>
+      </c>
+      <c r="C63" s="1">
+        <v>0</v>
+      </c>
+      <c r="D63" s="1">
+        <v>1</v>
+      </c>
+      <c r="E63" s="1">
+        <v>1</v>
+      </c>
+      <c r="F63" s="1">
+        <v>1</v>
+      </c>
+      <c r="G63" s="1">
+        <v>1</v>
+      </c>
+      <c r="H63" s="1">
+        <v>1</v>
+      </c>
+      <c r="I63" s="1">
+        <v>1</v>
+      </c>
+      <c r="J63" s="1">
+        <v>1</v>
+      </c>
+      <c r="K63" s="1">
+        <v>1</v>
+      </c>
+      <c r="L63" s="1">
+        <v>1</v>
+      </c>
+      <c r="M63" s="1">
+        <v>1</v>
+      </c>
+      <c r="N63" s="1">
+        <v>1</v>
+      </c>
+      <c r="O63" s="1">
+        <v>1</v>
+      </c>
+      <c r="P63" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q63" s="1">
+        <v>1</v>
+      </c>
+      <c r="R63" s="1">
+        <v>1</v>
+      </c>
+      <c r="S63" s="1">
+        <v>1</v>
+      </c>
+      <c r="T63" s="1">
+        <v>1</v>
+      </c>
+      <c r="U63" s="1">
+        <v>1</v>
+      </c>
+      <c r="V63" s="1">
+        <v>1</v>
+      </c>
+      <c r="W63" s="1">
+        <v>0</v>
+      </c>
+      <c r="X63" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>0</v>
+      </c>
+      <c r="B64" s="1">
+        <v>0</v>
+      </c>
+      <c r="C64" s="1">
+        <v>1</v>
+      </c>
+      <c r="D64" s="1">
+        <v>1</v>
+      </c>
+      <c r="E64" s="1">
+        <v>1</v>
+      </c>
+      <c r="F64" s="1">
+        <v>1</v>
+      </c>
+      <c r="G64" s="1">
+        <v>1</v>
+      </c>
+      <c r="H64" s="1">
+        <v>1</v>
+      </c>
+      <c r="I64" s="1">
+        <v>1</v>
+      </c>
+      <c r="J64" s="1">
+        <v>1</v>
+      </c>
+      <c r="K64" s="1">
+        <v>1</v>
+      </c>
+      <c r="L64" s="1">
+        <v>1</v>
+      </c>
+      <c r="M64" s="1">
+        <v>1</v>
+      </c>
+      <c r="N64" s="1">
+        <v>1</v>
+      </c>
+      <c r="O64" s="1">
+        <v>1</v>
+      </c>
+      <c r="P64" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q64" s="1">
+        <v>1</v>
+      </c>
+      <c r="R64" s="1">
+        <v>1</v>
+      </c>
+      <c r="S64" s="1">
+        <v>1</v>
+      </c>
+      <c r="T64" s="1">
+        <v>1</v>
+      </c>
+      <c r="U64" s="1">
+        <v>1</v>
+      </c>
+      <c r="V64" s="1">
+        <v>1</v>
+      </c>
+      <c r="W64" s="1">
+        <v>1</v>
+      </c>
+      <c r="X64" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>0</v>
+      </c>
+      <c r="B65" s="1">
+        <v>0</v>
+      </c>
+      <c r="C65" s="1">
+        <v>1</v>
+      </c>
+      <c r="D65" s="1">
+        <v>1</v>
+      </c>
+      <c r="E65" s="1">
+        <v>1</v>
+      </c>
+      <c r="F65" s="1">
+        <v>1</v>
+      </c>
+      <c r="G65" s="1">
+        <v>1</v>
+      </c>
+      <c r="H65" s="1">
+        <v>1</v>
+      </c>
+      <c r="I65" s="1">
+        <v>1</v>
+      </c>
+      <c r="J65" s="1">
+        <v>1</v>
+      </c>
+      <c r="K65" s="1">
+        <v>1</v>
+      </c>
+      <c r="L65" s="1">
+        <v>1</v>
+      </c>
+      <c r="M65" s="1">
+        <v>1</v>
+      </c>
+      <c r="N65" s="1">
+        <v>1</v>
+      </c>
+      <c r="O65" s="1">
+        <v>1</v>
+      </c>
+      <c r="P65" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q65" s="1">
+        <v>1</v>
+      </c>
+      <c r="R65" s="1">
+        <v>1</v>
+      </c>
+      <c r="S65" s="1">
+        <v>1</v>
+      </c>
+      <c r="T65" s="1">
+        <v>1</v>
+      </c>
+      <c r="U65" s="1">
+        <v>1</v>
+      </c>
+      <c r="V65" s="1">
+        <v>1</v>
+      </c>
+      <c r="W65" s="1">
+        <v>1</v>
+      </c>
+      <c r="X65" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y65" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>0</v>
+      </c>
+      <c r="B66" s="1">
+        <v>0</v>
+      </c>
+      <c r="C66" s="1">
+        <v>1</v>
+      </c>
+      <c r="D66" s="1">
+        <v>1</v>
+      </c>
+      <c r="E66" s="1">
+        <v>1</v>
+      </c>
+      <c r="F66" s="1">
+        <v>1</v>
+      </c>
+      <c r="G66" s="1">
+        <v>1</v>
+      </c>
+      <c r="H66" s="1">
+        <v>1</v>
+      </c>
+      <c r="I66" s="1">
+        <v>1</v>
+      </c>
+      <c r="J66" s="1">
+        <v>1</v>
+      </c>
+      <c r="K66" s="1">
+        <v>1</v>
+      </c>
+      <c r="L66" s="1">
+        <v>1</v>
+      </c>
+      <c r="M66" s="1">
+        <v>1</v>
+      </c>
+      <c r="N66" s="1">
+        <v>1</v>
+      </c>
+      <c r="O66" s="1">
+        <v>1</v>
+      </c>
+      <c r="P66" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q66" s="1">
+        <v>1</v>
+      </c>
+      <c r="R66" s="1">
+        <v>1</v>
+      </c>
+      <c r="S66" s="1">
+        <v>1</v>
+      </c>
+      <c r="T66" s="1">
+        <v>1</v>
+      </c>
+      <c r="U66" s="1">
+        <v>1</v>
+      </c>
+      <c r="V66" s="1">
+        <v>1</v>
+      </c>
+      <c r="W66" s="1">
+        <v>1</v>
+      </c>
+      <c r="X66" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y66" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>0</v>
+      </c>
+      <c r="B67" s="1">
+        <v>0</v>
+      </c>
+      <c r="C67" s="1">
+        <v>1</v>
+      </c>
+      <c r="D67" s="1">
+        <v>1</v>
+      </c>
+      <c r="E67" s="1">
+        <v>1</v>
+      </c>
+      <c r="F67" s="1">
+        <v>1</v>
+      </c>
+      <c r="G67" s="1">
+        <v>1</v>
+      </c>
+      <c r="H67" s="1">
+        <v>1</v>
+      </c>
+      <c r="I67" s="1">
+        <v>1</v>
+      </c>
+      <c r="J67" s="1">
+        <v>1</v>
+      </c>
+      <c r="K67" s="1">
+        <v>1</v>
+      </c>
+      <c r="L67" s="1">
+        <v>1</v>
+      </c>
+      <c r="M67" s="1">
+        <v>1</v>
+      </c>
+      <c r="N67" s="1">
+        <v>1</v>
+      </c>
+      <c r="O67" s="1">
+        <v>1</v>
+      </c>
+      <c r="P67" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q67" s="1">
+        <v>1</v>
+      </c>
+      <c r="R67" s="1">
+        <v>1</v>
+      </c>
+      <c r="S67" s="1">
+        <v>1</v>
+      </c>
+      <c r="T67" s="1">
+        <v>1</v>
+      </c>
+      <c r="U67" s="1">
+        <v>1</v>
+      </c>
+      <c r="V67" s="1">
+        <v>1</v>
+      </c>
+      <c r="W67" s="1">
+        <v>1</v>
+      </c>
+      <c r="X67" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y67" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>0</v>
+      </c>
+      <c r="B68" s="1">
+        <v>0</v>
+      </c>
+      <c r="C68" s="1">
+        <v>1</v>
+      </c>
+      <c r="D68" s="1">
+        <v>1</v>
+      </c>
+      <c r="E68" s="1">
+        <v>1</v>
+      </c>
+      <c r="F68" s="1">
+        <v>1</v>
+      </c>
+      <c r="G68" s="1">
+        <v>1</v>
+      </c>
+      <c r="H68" s="1">
+        <v>1</v>
+      </c>
+      <c r="I68" s="1">
+        <v>1</v>
+      </c>
+      <c r="J68" s="1">
+        <v>1</v>
+      </c>
+      <c r="K68" s="1">
+        <v>1</v>
+      </c>
+      <c r="L68" s="1">
+        <v>1</v>
+      </c>
+      <c r="M68" s="1">
+        <v>1</v>
+      </c>
+      <c r="N68" s="1">
+        <v>1</v>
+      </c>
+      <c r="O68" s="1">
+        <v>1</v>
+      </c>
+      <c r="P68" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q68" s="1">
+        <v>1</v>
+      </c>
+      <c r="R68" s="1">
+        <v>1</v>
+      </c>
+      <c r="S68" s="1">
+        <v>1</v>
+      </c>
+      <c r="T68" s="1">
+        <v>1</v>
+      </c>
+      <c r="U68" s="1">
+        <v>1</v>
+      </c>
+      <c r="V68" s="1">
+        <v>1</v>
+      </c>
+      <c r="W68" s="1">
+        <v>1</v>
+      </c>
+      <c r="X68" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y68" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>0</v>
+      </c>
+      <c r="B69" s="1">
+        <v>0</v>
+      </c>
+      <c r="C69" s="1">
+        <v>1</v>
+      </c>
+      <c r="D69" s="1">
+        <v>1</v>
+      </c>
+      <c r="E69" s="1">
+        <v>1</v>
+      </c>
+      <c r="F69" s="1">
+        <v>1</v>
+      </c>
+      <c r="G69" s="1">
+        <v>1</v>
+      </c>
+      <c r="H69" s="1">
+        <v>1</v>
+      </c>
+      <c r="I69" s="1">
+        <v>1</v>
+      </c>
+      <c r="J69" s="1">
+        <v>1</v>
+      </c>
+      <c r="K69" s="1">
+        <v>1</v>
+      </c>
+      <c r="L69" s="1">
+        <v>1</v>
+      </c>
+      <c r="M69" s="1">
+        <v>1</v>
+      </c>
+      <c r="N69" s="1">
+        <v>1</v>
+      </c>
+      <c r="O69" s="1">
+        <v>1</v>
+      </c>
+      <c r="P69" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q69" s="1">
+        <v>1</v>
+      </c>
+      <c r="R69" s="1">
+        <v>1</v>
+      </c>
+      <c r="S69" s="1">
+        <v>1</v>
+      </c>
+      <c r="T69" s="1">
+        <v>1</v>
+      </c>
+      <c r="U69" s="1">
+        <v>1</v>
+      </c>
+      <c r="V69" s="1">
+        <v>1</v>
+      </c>
+      <c r="W69" s="1">
+        <v>1</v>
+      </c>
+      <c r="X69" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y69" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>0</v>
+      </c>
+      <c r="B70" s="1">
+        <v>0</v>
+      </c>
+      <c r="C70" s="1">
+        <v>0</v>
+      </c>
+      <c r="D70" s="1">
+        <v>1</v>
+      </c>
+      <c r="E70" s="1">
+        <v>1</v>
+      </c>
+      <c r="F70" s="1">
+        <v>1</v>
+      </c>
+      <c r="G70" s="1">
+        <v>1</v>
+      </c>
+      <c r="H70" s="1">
+        <v>1</v>
+      </c>
+      <c r="I70" s="1">
+        <v>1</v>
+      </c>
+      <c r="J70" s="1">
+        <v>1</v>
+      </c>
+      <c r="K70" s="1">
+        <v>1</v>
+      </c>
+      <c r="L70" s="1">
+        <v>1</v>
+      </c>
+      <c r="M70" s="1">
+        <v>1</v>
+      </c>
+      <c r="N70" s="1">
+        <v>1</v>
+      </c>
+      <c r="O70" s="1">
+        <v>1</v>
+      </c>
+      <c r="P70" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q70" s="1">
+        <v>1</v>
+      </c>
+      <c r="R70" s="1">
+        <v>1</v>
+      </c>
+      <c r="S70" s="1">
+        <v>1</v>
+      </c>
+      <c r="T70" s="1">
+        <v>1</v>
+      </c>
+      <c r="U70" s="1">
+        <v>1</v>
+      </c>
+      <c r="V70" s="1">
+        <v>1</v>
+      </c>
+      <c r="W70" s="1">
+        <v>1</v>
+      </c>
+      <c r="X70" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>0</v>
+      </c>
+      <c r="B71" s="1">
+        <v>0</v>
+      </c>
+      <c r="C71" s="1">
+        <v>0</v>
+      </c>
+      <c r="D71" s="1">
+        <v>0</v>
+      </c>
+      <c r="E71" s="1">
+        <v>1</v>
+      </c>
+      <c r="F71" s="1">
+        <v>1</v>
+      </c>
+      <c r="G71" s="1">
+        <v>1</v>
+      </c>
+      <c r="H71" s="1">
+        <v>1</v>
+      </c>
+      <c r="I71" s="1">
+        <v>1</v>
+      </c>
+      <c r="J71" s="1">
+        <v>1</v>
+      </c>
+      <c r="K71" s="1">
+        <v>1</v>
+      </c>
+      <c r="L71" s="1">
+        <v>1</v>
+      </c>
+      <c r="M71" s="1">
+        <v>1</v>
+      </c>
+      <c r="N71" s="1">
+        <v>1</v>
+      </c>
+      <c r="O71" s="1">
+        <v>1</v>
+      </c>
+      <c r="P71" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q71" s="1">
+        <v>1</v>
+      </c>
+      <c r="R71" s="1">
+        <v>1</v>
+      </c>
+      <c r="S71" s="1">
+        <v>1</v>
+      </c>
+      <c r="T71" s="1">
+        <v>1</v>
+      </c>
+      <c r="U71" s="1">
+        <v>1</v>
+      </c>
+      <c r="V71" s="1">
+        <v>0</v>
+      </c>
+      <c r="W71" s="1">
+        <v>0</v>
+      </c>
+      <c r="X71" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>0</v>
+      </c>
+      <c r="B72" s="1">
+        <v>0</v>
+      </c>
+      <c r="C72" s="1">
+        <v>0</v>
+      </c>
+      <c r="D72" s="1">
+        <v>0</v>
+      </c>
+      <c r="E72" s="1">
+        <v>0</v>
+      </c>
+      <c r="F72" s="1">
+        <v>1</v>
+      </c>
+      <c r="G72" s="1">
+        <v>1</v>
+      </c>
+      <c r="H72" s="1">
+        <v>1</v>
+      </c>
+      <c r="I72" s="1">
+        <v>1</v>
+      </c>
+      <c r="J72" s="1">
+        <v>1</v>
+      </c>
+      <c r="K72" s="1">
+        <v>1</v>
+      </c>
+      <c r="L72" s="1">
+        <v>1</v>
+      </c>
+      <c r="M72" s="1">
+        <v>1</v>
+      </c>
+      <c r="N72" s="1">
+        <v>1</v>
+      </c>
+      <c r="O72" s="1">
+        <v>1</v>
+      </c>
+      <c r="P72" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q72" s="1">
+        <v>1</v>
+      </c>
+      <c r="R72" s="1">
+        <v>1</v>
+      </c>
+      <c r="S72" s="1">
+        <v>1</v>
+      </c>
+      <c r="T72" s="1">
+        <v>1</v>
+      </c>
+      <c r="U72" s="1">
+        <v>1</v>
+      </c>
+      <c r="V72" s="1">
+        <v>0</v>
+      </c>
+      <c r="W72" s="1">
+        <v>0</v>
+      </c>
+      <c r="X72" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y72" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
+        <v>0</v>
+      </c>
+      <c r="B73" s="1">
+        <v>0</v>
+      </c>
+      <c r="C73" s="1">
+        <v>0</v>
+      </c>
+      <c r="D73" s="1">
+        <v>0</v>
+      </c>
+      <c r="E73" s="1">
+        <v>0</v>
+      </c>
+      <c r="F73" s="1">
+        <v>0</v>
+      </c>
+      <c r="G73" s="1">
+        <v>0</v>
+      </c>
+      <c r="H73" s="1">
+        <v>0</v>
+      </c>
+      <c r="I73" s="1">
+        <v>0</v>
+      </c>
+      <c r="J73" s="1">
+        <v>1</v>
+      </c>
+      <c r="K73" s="1">
+        <v>1</v>
+      </c>
+      <c r="L73" s="1">
+        <v>1</v>
+      </c>
+      <c r="M73" s="1">
+        <v>1</v>
+      </c>
+      <c r="N73" s="1">
+        <v>1</v>
+      </c>
+      <c r="O73" s="1">
+        <v>1</v>
+      </c>
+      <c r="P73" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q73" s="1">
+        <v>1</v>
+      </c>
+      <c r="R73" s="1">
+        <v>1</v>
+      </c>
+      <c r="S73" s="1">
+        <v>1</v>
+      </c>
+      <c r="T73" s="1">
+        <v>1</v>
+      </c>
+      <c r="U73" s="1">
+        <v>0</v>
+      </c>
+      <c r="V73" s="1">
+        <v>0</v>
+      </c>
+      <c r="W73" s="1">
+        <v>0</v>
+      </c>
+      <c r="X73" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
+        <v>0</v>
+      </c>
+      <c r="B74" s="1">
+        <v>0</v>
+      </c>
+      <c r="C74" s="1">
+        <v>0</v>
+      </c>
+      <c r="D74" s="1">
+        <v>0</v>
+      </c>
+      <c r="E74" s="1">
+        <v>0</v>
+      </c>
+      <c r="F74" s="1">
+        <v>0</v>
+      </c>
+      <c r="G74" s="1">
+        <v>0</v>
+      </c>
+      <c r="H74" s="1">
+        <v>0</v>
+      </c>
+      <c r="I74" s="1">
+        <v>0</v>
+      </c>
+      <c r="J74" s="1">
+        <v>0</v>
+      </c>
+      <c r="K74" s="1">
+        <v>0</v>
+      </c>
+      <c r="L74" s="1">
+        <v>0</v>
+      </c>
+      <c r="M74" s="1">
+        <v>1</v>
+      </c>
+      <c r="N74" s="1">
+        <v>1</v>
+      </c>
+      <c r="O74" s="1">
+        <v>1</v>
+      </c>
+      <c r="P74" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q74" s="1">
+        <v>1</v>
+      </c>
+      <c r="R74" s="1">
+        <v>1</v>
+      </c>
+      <c r="S74" s="1">
+        <v>1</v>
+      </c>
+      <c r="T74" s="1">
+        <v>1</v>
+      </c>
+      <c r="U74" s="1">
+        <v>0</v>
+      </c>
+      <c r="V74" s="1">
+        <v>0</v>
+      </c>
+      <c r="W74" s="1">
+        <v>0</v>
+      </c>
+      <c r="X74" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
+        <v>0</v>
+      </c>
+      <c r="B75" s="1">
+        <v>0</v>
+      </c>
+      <c r="C75" s="1">
+        <v>0</v>
+      </c>
+      <c r="D75" s="1">
+        <v>0</v>
+      </c>
+      <c r="E75" s="1">
+        <v>0</v>
+      </c>
+      <c r="F75" s="1">
+        <v>0</v>
+      </c>
+      <c r="G75" s="1">
+        <v>0</v>
+      </c>
+      <c r="H75" s="1">
+        <v>0</v>
+      </c>
+      <c r="I75" s="1">
+        <v>0</v>
+      </c>
+      <c r="J75" s="1">
+        <v>0</v>
+      </c>
+      <c r="K75" s="1">
+        <v>0</v>
+      </c>
+      <c r="L75" s="1">
+        <v>0</v>
+      </c>
+      <c r="M75" s="1">
+        <v>0</v>
+      </c>
+      <c r="N75" s="1">
+        <v>0</v>
+      </c>
+      <c r="O75" s="1">
+        <v>0</v>
+      </c>
+      <c r="P75" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="1">
+        <v>0</v>
+      </c>
+      <c r="R75" s="1">
+        <v>0</v>
+      </c>
+      <c r="S75" s="1">
+        <v>0</v>
+      </c>
+      <c r="T75" s="1">
+        <v>0</v>
+      </c>
+      <c r="U75" s="1">
+        <v>0</v>
+      </c>
+      <c r="V75" s="1">
+        <v>0</v>
+      </c>
+      <c r="W75" s="1">
+        <v>0</v>
+      </c>
+      <c r="X75" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
+        <v>0</v>
+      </c>
+      <c r="B76" s="1">
+        <v>0</v>
+      </c>
+      <c r="C76" s="1">
+        <v>0</v>
+      </c>
+      <c r="D76" s="1">
+        <v>0</v>
+      </c>
+      <c r="E76" s="1">
+        <v>0</v>
+      </c>
+      <c r="F76" s="1">
+        <v>0</v>
+      </c>
+      <c r="G76" s="1">
+        <v>0</v>
+      </c>
+      <c r="H76" s="1">
+        <v>0</v>
+      </c>
+      <c r="I76" s="1">
+        <v>0</v>
+      </c>
+      <c r="J76" s="1">
+        <v>0</v>
+      </c>
+      <c r="K76" s="1">
+        <v>0</v>
+      </c>
+      <c r="L76" s="1">
+        <v>0</v>
+      </c>
+      <c r="M76" s="1">
+        <v>0</v>
+      </c>
+      <c r="N76" s="1">
+        <v>0</v>
+      </c>
+      <c r="O76" s="1">
+        <v>0</v>
+      </c>
+      <c r="P76" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="1">
+        <v>0</v>
+      </c>
+      <c r="R76" s="1">
+        <v>0</v>
+      </c>
+      <c r="S76" s="1">
+        <v>0</v>
+      </c>
+      <c r="T76" s="1">
+        <v>0</v>
+      </c>
+      <c r="U76" s="1">
+        <v>0</v>
+      </c>
+      <c r="V76" s="1">
+        <v>0</v>
+      </c>
+      <c r="W76" s="1">
+        <v>0</v>
+      </c>
+      <c r="X76" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y76" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <v>0</v>
+      </c>
+      <c r="B77" s="1">
+        <v>0</v>
+      </c>
+      <c r="C77" s="1">
+        <v>0</v>
+      </c>
+      <c r="D77" s="1">
+        <v>0</v>
+      </c>
+      <c r="E77" s="1">
+        <v>0</v>
+      </c>
+      <c r="F77" s="1">
+        <v>0</v>
+      </c>
+      <c r="G77" s="1">
+        <v>0</v>
+      </c>
+      <c r="H77" s="1">
+        <v>0</v>
+      </c>
+      <c r="I77" s="1">
+        <v>0</v>
+      </c>
+      <c r="J77" s="1">
+        <v>0</v>
+      </c>
+      <c r="K77" s="1">
+        <v>0</v>
+      </c>
+      <c r="L77" s="1">
+        <v>0</v>
+      </c>
+      <c r="M77" s="1">
+        <v>0</v>
+      </c>
+      <c r="N77" s="1">
+        <v>0</v>
+      </c>
+      <c r="O77" s="1">
+        <v>0</v>
+      </c>
+      <c r="P77" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="1">
+        <v>0</v>
+      </c>
+      <c r="R77" s="1">
+        <v>0</v>
+      </c>
+      <c r="S77" s="1">
+        <v>0</v>
+      </c>
+      <c r="T77" s="1">
+        <v>0</v>
+      </c>
+      <c r="U77" s="1">
+        <v>0</v>
+      </c>
+      <c r="V77" s="1">
+        <v>0</v>
+      </c>
+      <c r="W77" s="1">
+        <v>0</v>
+      </c>
+      <c r="X77" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
+        <v>0</v>
+      </c>
+      <c r="B78" s="1">
+        <v>0</v>
+      </c>
+      <c r="C78" s="1">
+        <v>0</v>
+      </c>
+      <c r="D78" s="1">
+        <v>0</v>
+      </c>
+      <c r="E78" s="1">
+        <v>0</v>
+      </c>
+      <c r="F78" s="1">
+        <v>0</v>
+      </c>
+      <c r="G78" s="1">
+        <v>0</v>
+      </c>
+      <c r="H78" s="1">
+        <v>0</v>
+      </c>
+      <c r="I78" s="1">
+        <v>0</v>
+      </c>
+      <c r="J78" s="1">
+        <v>0</v>
+      </c>
+      <c r="K78" s="1">
+        <v>0</v>
+      </c>
+      <c r="L78" s="1">
+        <v>0</v>
+      </c>
+      <c r="M78" s="1">
+        <v>0</v>
+      </c>
+      <c r="N78" s="1">
+        <v>0</v>
+      </c>
+      <c r="O78" s="1">
+        <v>0</v>
+      </c>
+      <c r="P78" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="1">
+        <v>0</v>
+      </c>
+      <c r="R78" s="1">
+        <v>0</v>
+      </c>
+      <c r="S78" s="1">
+        <v>0</v>
+      </c>
+      <c r="T78" s="1">
+        <v>0</v>
+      </c>
+      <c r="U78" s="1">
+        <v>0</v>
+      </c>
+      <c r="V78" s="1">
+        <v>0</v>
+      </c>
+      <c r="W78" s="1">
+        <v>0</v>
+      </c>
+      <c r="X78" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y78" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
+        <v>0</v>
+      </c>
+      <c r="B79" s="1">
+        <v>0</v>
+      </c>
+      <c r="C79" s="1">
+        <v>0</v>
+      </c>
+      <c r="D79" s="1">
+        <v>0</v>
+      </c>
+      <c r="E79" s="1">
+        <v>0</v>
+      </c>
+      <c r="F79" s="1">
+        <v>0</v>
+      </c>
+      <c r="G79" s="1">
+        <v>0</v>
+      </c>
+      <c r="H79" s="1">
+        <v>0</v>
+      </c>
+      <c r="I79" s="1">
+        <v>0</v>
+      </c>
+      <c r="J79" s="1">
+        <v>0</v>
+      </c>
+      <c r="K79" s="1">
+        <v>0</v>
+      </c>
+      <c r="L79" s="1">
+        <v>0</v>
+      </c>
+      <c r="M79" s="1">
+        <v>0</v>
+      </c>
+      <c r="N79" s="1">
+        <v>0</v>
+      </c>
+      <c r="O79" s="1">
+        <v>0</v>
+      </c>
+      <c r="P79" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="1">
+        <v>0</v>
+      </c>
+      <c r="R79" s="1">
+        <v>0</v>
+      </c>
+      <c r="S79" s="1">
+        <v>0</v>
+      </c>
+      <c r="T79" s="1">
+        <v>0</v>
+      </c>
+      <c r="U79" s="1">
+        <v>0</v>
+      </c>
+      <c r="V79" s="1">
+        <v>0</v>
+      </c>
+      <c r="W79" s="1">
+        <v>0</v>
+      </c>
+      <c r="X79" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y79" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="81" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="82" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="83" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5879,67 +7365,92 @@
     <row r="113" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <conditionalFormatting sqref="A27:A29">
-    <cfRule type="cellIs" dxfId="12" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="12" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:A49">
-    <cfRule type="cellIs" dxfId="11" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="16" priority="13" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:Y17 A20:Y58">
-    <cfRule type="cellIs" dxfId="10" priority="17" operator="greaterThan">
+  <conditionalFormatting sqref="A20:Y58 A1:Y17">
+    <cfRule type="cellIs" dxfId="15" priority="22" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:Y19">
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="8" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18:Y19">
-    <cfRule type="cellIs" dxfId="8" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="9" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:Y20">
-    <cfRule type="cellIs" dxfId="7" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="20" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:Y58 A60:Y60">
-    <cfRule type="cellIs" dxfId="6" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="21" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40:Y40">
-    <cfRule type="cellIs" dxfId="5" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="19" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59:Y59">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="6" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A59:Y60">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="7" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A60:Y60">
-    <cfRule type="cellIs" dxfId="2" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="18" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y6:Y8">
-    <cfRule type="cellIs" dxfId="1" priority="10" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="15" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y28:Y30">
-    <cfRule type="cellIs" dxfId="0" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="14" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A61:Y77">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A61:Y79">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A78:Y79">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y66:Y68">
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A7">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
